--- a/ic_cad/gate_sizing/Test_Result_cadc1006.xlsx
+++ b/ic_cad/gate_sizing/Test_Result_cadc1006.xlsx
@@ -475,12 +475,14 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C25"/>
+  <dimension ref="A1:E25"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
     <col width="25" customWidth="1" min="2" max="2"/>
     <col width="21" customWidth="1" min="3" max="3"/>
+    <col width="21" customWidth="1" min="4" max="4"/>
+    <col width="21" customWidth="1" min="5" max="5"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -499,6 +501,8 @@
           <t>visible benchmarks</t>
         </is>
       </c>
+      <c r="D1" s="1" t="n"/>
+      <c r="E1" s="1" t="n"/>
     </row>
     <row r="2">
       <c r="A2" s="2" t="inlineStr"/>
@@ -508,6 +512,16 @@
           <t>aes_cipher_top</t>
         </is>
       </c>
+      <c r="D2" s="2" t="inlineStr">
+        <is>
+          <t>aes</t>
+        </is>
+      </c>
+      <c r="E2" s="2" t="inlineStr">
+        <is>
+          <t>des</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" s="3" t="inlineStr">
@@ -521,6 +535,16 @@
         </is>
       </c>
       <c r="C3" s="4" t="inlineStr">
+        <is>
+          <t>7.00</t>
+        </is>
+      </c>
+      <c r="D3" s="4" t="inlineStr">
+        <is>
+          <t>7.00</t>
+        </is>
+      </c>
+      <c r="E3" s="4" t="inlineStr">
         <is>
           <t>7.00</t>
         </is>
@@ -535,7 +559,17 @@
       </c>
       <c r="C4" s="4" t="inlineStr">
         <is>
-          <t>-24870.38</t>
+          <t>-14574.96</t>
+        </is>
+      </c>
+      <c r="D4" s="4" t="inlineStr">
+        <is>
+          <t>-9214.42</t>
+        </is>
+      </c>
+      <c r="E4" s="4" t="inlineStr">
+        <is>
+          <t>-2107.30</t>
         </is>
       </c>
     </row>
@@ -548,7 +582,17 @@
       </c>
       <c r="C5" s="4" t="inlineStr">
         <is>
-          <t>-126.93</t>
+          <t>-93.07</t>
+        </is>
+      </c>
+      <c r="D5" s="4" t="inlineStr">
+        <is>
+          <t>-62.21</t>
+        </is>
+      </c>
+      <c r="E5" s="4" t="inlineStr">
+        <is>
+          <t>-72.49</t>
         </is>
       </c>
     </row>
@@ -561,7 +605,17 @@
       </c>
       <c r="C6" s="4" t="inlineStr">
         <is>
-          <t>7.69</t>
+          <t>7.83</t>
+        </is>
+      </c>
+      <c r="D6" s="4" t="inlineStr">
+        <is>
+          <t>4.20</t>
+        </is>
+      </c>
+      <c r="E6" s="4" t="inlineStr">
+        <is>
+          <t>1.58</t>
         </is>
       </c>
     </row>
@@ -574,7 +628,17 @@
       </c>
       <c r="C7" s="4" t="inlineStr">
         <is>
-          <t>38997558.00</t>
+          <t>38388384.00</t>
+        </is>
+      </c>
+      <c r="D7" s="4" t="inlineStr">
+        <is>
+          <t>16707222.00</t>
+        </is>
+      </c>
+      <c r="E7" s="4" t="inlineStr">
+        <is>
+          <t>5402214.00</t>
         </is>
       </c>
     </row>
@@ -587,7 +651,17 @@
       </c>
       <c r="C8" s="5" t="inlineStr">
         <is>
-          <t>19.84</t>
+          <t>0.00</t>
+        </is>
+      </c>
+      <c r="D8" s="5" t="inlineStr">
+        <is>
+          <t>0.00</t>
+        </is>
+      </c>
+      <c r="E8" s="5" t="inlineStr">
+        <is>
+          <t>0.54</t>
         </is>
       </c>
     </row>
@@ -603,6 +677,16 @@
           <t>-13971.28</t>
         </is>
       </c>
+      <c r="D9" s="6" t="inlineStr">
+        <is>
+          <t>-6833.96</t>
+        </is>
+      </c>
+      <c r="E9" s="6" t="inlineStr">
+        <is>
+          <t>-2049.19</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" s="4" t="n"/>
@@ -616,6 +700,16 @@
           <t>-93.91</t>
         </is>
       </c>
+      <c r="D10" s="6" t="inlineStr">
+        <is>
+          <t>-62.31</t>
+        </is>
+      </c>
+      <c r="E10" s="6" t="inlineStr">
+        <is>
+          <t>-71.60</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" s="4" t="n"/>
@@ -629,6 +723,16 @@
           <t>7.86</t>
         </is>
       </c>
+      <c r="D11" s="6" t="inlineStr">
+        <is>
+          <t>4.34</t>
+        </is>
+      </c>
+      <c r="E11" s="6" t="inlineStr">
+        <is>
+          <t>1.58</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" s="5" t="n"/>
@@ -642,6 +746,16 @@
           <t>38388384.00</t>
         </is>
       </c>
+      <c r="D12" s="7" t="inlineStr">
+        <is>
+          <t>16707222.00</t>
+        </is>
+      </c>
+      <c r="E12" s="7" t="inlineStr">
+        <is>
+          <t>5401080.00</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" s="4" t="n"/>
@@ -652,7 +766,17 @@
       </c>
       <c r="C13" s="4" t="inlineStr">
         <is>
-          <t>-0.780108</t>
+          <t>-0.043209</t>
+        </is>
+      </c>
+      <c r="D13" s="4" t="inlineStr">
+        <is>
+          <t>-0.348329</t>
+        </is>
+      </c>
+      <c r="E13" s="4" t="inlineStr">
+        <is>
+          <t>-0.028359</t>
         </is>
       </c>
     </row>
@@ -665,7 +789,17 @@
       </c>
       <c r="C14" s="4" t="inlineStr">
         <is>
-          <t>0.021416</t>
+          <t>0.003476</t>
+        </is>
+      </c>
+      <c r="D14" s="4" t="inlineStr">
+        <is>
+          <t>0.030878</t>
+        </is>
+      </c>
+      <c r="E14" s="4" t="inlineStr">
+        <is>
+          <t>0.002359</t>
         </is>
       </c>
     </row>
@@ -678,7 +812,17 @@
       </c>
       <c r="C15" s="4" t="inlineStr">
         <is>
-          <t>-0.015869</t>
+          <t>0.000000</t>
+        </is>
+      </c>
+      <c r="D15" s="4" t="inlineStr">
+        <is>
+          <t>0.000000</t>
+        </is>
+      </c>
+      <c r="E15" s="4" t="inlineStr">
+        <is>
+          <t>-0.000210</t>
         </is>
       </c>
     </row>
@@ -691,7 +835,17 @@
       </c>
       <c r="C16" s="4" t="inlineStr">
         <is>
-          <t>0.019836</t>
+          <t>0.000000</t>
+        </is>
+      </c>
+      <c r="D16" s="4" t="inlineStr">
+        <is>
+          <t>0.000000</t>
+        </is>
+      </c>
+      <c r="E16" s="4" t="inlineStr">
+        <is>
+          <t>0.000536</t>
         </is>
       </c>
     </row>
@@ -707,6 +861,16 @@
           <t>0.001944</t>
         </is>
       </c>
+      <c r="D17" s="4" t="inlineStr">
+        <is>
+          <t>0.001944</t>
+        </is>
+      </c>
+      <c r="E17" s="4" t="inlineStr">
+        <is>
+          <t>0.001944</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" s="5" t="n"/>
@@ -717,7 +881,17 @@
       </c>
       <c r="C18" s="5" t="inlineStr">
         <is>
-          <t>-0.263406</t>
+          <t>-0.013544</t>
+        </is>
+      </c>
+      <c r="D18" s="5" t="inlineStr">
+        <is>
+          <t>-0.108242</t>
+        </is>
+      </c>
+      <c r="E18" s="5" t="inlineStr">
+        <is>
+          <t>-0.008933</t>
         </is>
       </c>
     </row>
@@ -730,7 +904,17 @@
       </c>
       <c r="C19" s="8" t="inlineStr">
         <is>
-          <t>-264.456320</t>
+          <t>-13.602218</t>
+        </is>
+      </c>
+      <c r="D19" s="8" t="inlineStr">
+        <is>
+          <t>-108.300244</t>
+        </is>
+      </c>
+      <c r="E19" s="8" t="inlineStr">
+        <is>
+          <t>-9.017999</t>
         </is>
       </c>
     </row>
@@ -746,6 +930,16 @@
           <t>2025-09-11 01:35:14</t>
         </is>
       </c>
+      <c r="D20" s="4" t="inlineStr">
+        <is>
+          <t>2025-09-11 01:35:14</t>
+        </is>
+      </c>
+      <c r="E20" s="4" t="inlineStr">
+        <is>
+          <t>2025-09-11 01:35:14</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" s="5" t="n"/>
@@ -759,6 +953,16 @@
           <t>0.00</t>
         </is>
       </c>
+      <c r="D21" s="5" t="inlineStr">
+        <is>
+          <t>0.00</t>
+        </is>
+      </c>
+      <c r="E21" s="5" t="inlineStr">
+        <is>
+          <t>0.00</t>
+        </is>
+      </c>
     </row>
     <row r="22">
       <c r="A22" s="4" t="n"/>
@@ -772,6 +976,16 @@
           <t>1179.00</t>
         </is>
       </c>
+      <c r="D22" s="4" t="inlineStr">
+        <is>
+          <t>627.00</t>
+        </is>
+      </c>
+      <c r="E22" s="4" t="inlineStr">
+        <is>
+          <t>263.00</t>
+        </is>
+      </c>
     </row>
     <row r="23">
       <c r="A23" s="4" t="n"/>
@@ -785,6 +999,16 @@
           <t>71.20</t>
         </is>
       </c>
+      <c r="D23" s="4" t="inlineStr">
+        <is>
+          <t>64.70</t>
+        </is>
+      </c>
+      <c r="E23" s="4" t="inlineStr">
+        <is>
+          <t>68.20</t>
+        </is>
+      </c>
     </row>
     <row r="24">
       <c r="A24" s="4" t="n"/>
@@ -795,7 +1019,17 @@
       </c>
       <c r="C24" s="4" t="inlineStr">
         <is>
-          <t>1210.00</t>
+          <t>1179.00</t>
+        </is>
+      </c>
+      <c r="D24" s="4" t="inlineStr">
+        <is>
+          <t>627.00</t>
+        </is>
+      </c>
+      <c r="E24" s="4" t="inlineStr">
+        <is>
+          <t>263.00</t>
         </is>
       </c>
     </row>
@@ -808,7 +1042,17 @@
       </c>
       <c r="C25" s="4" t="inlineStr">
         <is>
-          <t>73.10</t>
+          <t>71.20</t>
+        </is>
+      </c>
+      <c r="D25" s="4" t="inlineStr">
+        <is>
+          <t>64.70</t>
+        </is>
+      </c>
+      <c r="E25" s="4" t="inlineStr">
+        <is>
+          <t>68.20</t>
         </is>
       </c>
     </row>

--- a/ic_cad/gate_sizing/Test_Result_cadc1006.xlsx
+++ b/ic_cad/gate_sizing/Test_Result_cadc1006.xlsx
@@ -475,7 +475,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E25"/>
+  <dimension ref="A1:G25"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
@@ -483,6 +483,8 @@
     <col width="21" customWidth="1" min="3" max="3"/>
     <col width="21" customWidth="1" min="4" max="4"/>
     <col width="21" customWidth="1" min="5" max="5"/>
+    <col width="21" customWidth="1" min="6" max="6"/>
+    <col width="21" customWidth="1" min="7" max="7"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -503,6 +505,8 @@
       </c>
       <c r="D1" s="1" t="n"/>
       <c r="E1" s="1" t="n"/>
+      <c r="F1" s="1" t="n"/>
+      <c r="G1" s="1" t="n"/>
     </row>
     <row r="2">
       <c r="A2" s="2" t="inlineStr"/>
@@ -522,6 +526,16 @@
           <t>des</t>
         </is>
       </c>
+      <c r="F2" s="2" t="inlineStr">
+        <is>
+          <t>ac97_top</t>
+        </is>
+      </c>
+      <c r="G2" s="2" t="inlineStr">
+        <is>
+          <t>pci_bridge32</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" s="3" t="inlineStr">
@@ -545,6 +559,16 @@
         </is>
       </c>
       <c r="E3" s="4" t="inlineStr">
+        <is>
+          <t>7.00</t>
+        </is>
+      </c>
+      <c r="F3" s="4" t="inlineStr">
+        <is>
+          <t>7.00</t>
+        </is>
+      </c>
+      <c r="G3" s="4" t="inlineStr">
         <is>
           <t>7.00</t>
         </is>
@@ -559,17 +583,27 @@
       </c>
       <c r="C4" s="4" t="inlineStr">
         <is>
-          <t>-14574.96</t>
+          <t>-14460.77</t>
         </is>
       </c>
       <c r="D4" s="4" t="inlineStr">
         <is>
-          <t>-9214.42</t>
+          <t>-13024.05</t>
         </is>
       </c>
       <c r="E4" s="4" t="inlineStr">
         <is>
-          <t>-2107.30</t>
+          <t>-2107.20</t>
+        </is>
+      </c>
+      <c r="F4" s="4" t="inlineStr">
+        <is>
+          <t>-197592.39</t>
+        </is>
+      </c>
+      <c r="G4" s="4" t="inlineStr">
+        <is>
+          <t>-337088.04</t>
         </is>
       </c>
     </row>
@@ -582,17 +616,27 @@
       </c>
       <c r="C5" s="4" t="inlineStr">
         <is>
-          <t>-93.07</t>
+          <t>-92.95</t>
         </is>
       </c>
       <c r="D5" s="4" t="inlineStr">
         <is>
-          <t>-62.21</t>
+          <t>-79.57</t>
         </is>
       </c>
       <c r="E5" s="4" t="inlineStr">
         <is>
           <t>-72.49</t>
+        </is>
+      </c>
+      <c r="F5" s="4" t="inlineStr">
+        <is>
+          <t>-293.17</t>
+        </is>
+      </c>
+      <c r="G5" s="4" t="inlineStr">
+        <is>
+          <t>-378.09</t>
         </is>
       </c>
     </row>
@@ -610,12 +654,22 @@
       </c>
       <c r="D6" s="4" t="inlineStr">
         <is>
-          <t>4.20</t>
+          <t>4.18</t>
         </is>
       </c>
       <c r="E6" s="4" t="inlineStr">
         <is>
           <t>1.58</t>
+        </is>
+      </c>
+      <c r="F6" s="4" t="inlineStr">
+        <is>
+          <t>12.97</t>
+        </is>
+      </c>
+      <c r="G6" s="4" t="inlineStr">
+        <is>
+          <t>11.53</t>
         </is>
       </c>
     </row>
@@ -641,6 +695,16 @@
           <t>5402214.00</t>
         </is>
       </c>
+      <c r="F7" s="4" t="inlineStr">
+        <is>
+          <t>21231828.00</t>
+        </is>
+      </c>
+      <c r="G7" s="4" t="inlineStr">
+        <is>
+          <t>43286130.00</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" s="5" t="n"/>
@@ -664,6 +728,16 @@
           <t>0.54</t>
         </is>
       </c>
+      <c r="F8" s="5" t="inlineStr">
+        <is>
+          <t>0.01</t>
+        </is>
+      </c>
+      <c r="G8" s="5" t="inlineStr">
+        <is>
+          <t>0.00</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" s="4" t="n"/>
@@ -687,6 +761,16 @@
           <t>-2049.19</t>
         </is>
       </c>
+      <c r="F9" s="6" t="inlineStr">
+        <is>
+          <t>-198213.16</t>
+        </is>
+      </c>
+      <c r="G9" s="6" t="inlineStr">
+        <is>
+          <t>-389996.70</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" s="4" t="n"/>
@@ -710,6 +794,16 @@
           <t>-71.60</t>
         </is>
       </c>
+      <c r="F10" s="6" t="inlineStr">
+        <is>
+          <t>-266.22</t>
+        </is>
+      </c>
+      <c r="G10" s="6" t="inlineStr">
+        <is>
+          <t>-476.48</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" s="4" t="n"/>
@@ -733,6 +827,16 @@
           <t>1.58</t>
         </is>
       </c>
+      <c r="F11" s="6" t="inlineStr">
+        <is>
+          <t>13.23</t>
+        </is>
+      </c>
+      <c r="G11" s="6" t="inlineStr">
+        <is>
+          <t>12.76</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" s="5" t="n"/>
@@ -756,6 +860,16 @@
           <t>5401080.00</t>
         </is>
       </c>
+      <c r="F12" s="7" t="inlineStr">
+        <is>
+          <t>21231828.00</t>
+        </is>
+      </c>
+      <c r="G12" s="7" t="inlineStr">
+        <is>
+          <t>43286184.00</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" s="4" t="n"/>
@@ -766,17 +880,27 @@
       </c>
       <c r="C13" s="4" t="inlineStr">
         <is>
-          <t>-0.043209</t>
+          <t>-0.035036</t>
         </is>
       </c>
       <c r="D13" s="4" t="inlineStr">
         <is>
-          <t>-0.348329</t>
+          <t>-0.905784</t>
         </is>
       </c>
       <c r="E13" s="4" t="inlineStr">
         <is>
-          <t>-0.028359</t>
+          <t>-0.028308</t>
+        </is>
+      </c>
+      <c r="F13" s="4" t="inlineStr">
+        <is>
+          <t>0.003132</t>
+        </is>
+      </c>
+      <c r="G13" s="4" t="inlineStr">
+        <is>
+          <t>0.135664</t>
         </is>
       </c>
     </row>
@@ -789,17 +913,27 @@
       </c>
       <c r="C14" s="4" t="inlineStr">
         <is>
-          <t>0.003476</t>
+          <t>0.003356</t>
         </is>
       </c>
       <c r="D14" s="4" t="inlineStr">
         <is>
-          <t>0.030878</t>
+          <t>0.037204</t>
         </is>
       </c>
       <c r="E14" s="4" t="inlineStr">
         <is>
-          <t>0.002359</t>
+          <t>0.001724</t>
+        </is>
+      </c>
+      <c r="F14" s="4" t="inlineStr">
+        <is>
+          <t>0.019457</t>
+        </is>
+      </c>
+      <c r="G14" s="4" t="inlineStr">
+        <is>
+          <t>0.096369</t>
         </is>
       </c>
     </row>
@@ -825,6 +959,16 @@
           <t>-0.000210</t>
         </is>
       </c>
+      <c r="F15" s="4" t="inlineStr">
+        <is>
+          <t>0.000000</t>
+        </is>
+      </c>
+      <c r="G15" s="4" t="inlineStr">
+        <is>
+          <t>0.000001</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" s="4" t="n"/>
@@ -848,6 +992,16 @@
           <t>0.000536</t>
         </is>
       </c>
+      <c r="F16" s="4" t="inlineStr">
+        <is>
+          <t>0.000007</t>
+        </is>
+      </c>
+      <c r="G16" s="4" t="inlineStr">
+        <is>
+          <t>0.000004</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" s="4" t="n"/>
@@ -871,6 +1025,16 @@
           <t>0.001944</t>
         </is>
       </c>
+      <c r="F17" s="4" t="inlineStr">
+        <is>
+          <t>0.001944</t>
+        </is>
+      </c>
+      <c r="G17" s="4" t="inlineStr">
+        <is>
+          <t>0.001944</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" s="5" t="n"/>
@@ -881,17 +1045,27 @@
       </c>
       <c r="C18" s="5" t="inlineStr">
         <is>
-          <t>-0.013544</t>
+          <t>-0.010805</t>
         </is>
       </c>
       <c r="D18" s="5" t="inlineStr">
         <is>
-          <t>-0.108242</t>
+          <t>-0.295689</t>
         </is>
       </c>
       <c r="E18" s="5" t="inlineStr">
         <is>
-          <t>-0.008933</t>
+          <t>-0.009125</t>
+        </is>
+      </c>
+      <c r="F18" s="5" t="inlineStr">
+        <is>
+          <t>0.007486</t>
+        </is>
+      </c>
+      <c r="G18" s="5" t="inlineStr">
+        <is>
+          <t>0.077928</t>
         </is>
       </c>
     </row>
@@ -904,17 +1078,27 @@
       </c>
       <c r="C19" s="8" t="inlineStr">
         <is>
-          <t>-13.602218</t>
+          <t>-10.862988</t>
         </is>
       </c>
       <c r="D19" s="8" t="inlineStr">
         <is>
-          <t>-108.300244</t>
+          <t>-295.747397</t>
         </is>
       </c>
       <c r="E19" s="8" t="inlineStr">
         <is>
-          <t>-9.017999</t>
+          <t>-9.210354</t>
+        </is>
+      </c>
+      <c r="F19" s="8" t="inlineStr">
+        <is>
+          <t>7.426912</t>
+        </is>
+      </c>
+      <c r="G19" s="8" t="inlineStr">
+        <is>
+          <t>77.869649</t>
         </is>
       </c>
     </row>
@@ -940,6 +1124,16 @@
           <t>2025-09-11 01:35:14</t>
         </is>
       </c>
+      <c r="F20" s="4" t="inlineStr">
+        <is>
+          <t>2025-09-11 01:35:14</t>
+        </is>
+      </c>
+      <c r="G20" s="4" t="inlineStr">
+        <is>
+          <t>2025-09-11 01:35:14</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" s="5" t="n"/>
@@ -963,6 +1157,16 @@
           <t>0.00</t>
         </is>
       </c>
+      <c r="F21" s="5" t="inlineStr">
+        <is>
+          <t>0.00</t>
+        </is>
+      </c>
+      <c r="G21" s="5" t="inlineStr">
+        <is>
+          <t>0.00</t>
+        </is>
+      </c>
     </row>
     <row r="22">
       <c r="A22" s="4" t="n"/>
@@ -986,6 +1190,16 @@
           <t>263.00</t>
         </is>
       </c>
+      <c r="F22" s="4" t="inlineStr">
+        <is>
+          <t>1179.00</t>
+        </is>
+      </c>
+      <c r="G22" s="4" t="inlineStr">
+        <is>
+          <t>1914.00</t>
+        </is>
+      </c>
     </row>
     <row r="23">
       <c r="A23" s="4" t="n"/>
@@ -1009,6 +1223,16 @@
           <t>68.20</t>
         </is>
       </c>
+      <c r="F23" s="4" t="inlineStr">
+        <is>
+          <t>61.60</t>
+        </is>
+      </c>
+      <c r="G23" s="4" t="inlineStr">
+        <is>
+          <t>64.00</t>
+        </is>
+      </c>
     </row>
     <row r="24">
       <c r="A24" s="4" t="n"/>
@@ -1032,6 +1256,16 @@
           <t>263.00</t>
         </is>
       </c>
+      <c r="F24" s="4" t="inlineStr">
+        <is>
+          <t>1179.00</t>
+        </is>
+      </c>
+      <c r="G24" s="4" t="inlineStr">
+        <is>
+          <t>1914.00</t>
+        </is>
+      </c>
     </row>
     <row r="25">
       <c r="A25" s="4" t="n"/>
@@ -1053,6 +1287,16 @@
       <c r="E25" s="4" t="inlineStr">
         <is>
           <t>68.20</t>
+        </is>
+      </c>
+      <c r="F25" s="4" t="inlineStr">
+        <is>
+          <t>61.60</t>
+        </is>
+      </c>
+      <c r="G25" s="4" t="inlineStr">
+        <is>
+          <t>64.00</t>
         </is>
       </c>
     </row>

--- a/ic_cad/gate_sizing/Test_Result_cadc1006.xlsx
+++ b/ic_cad/gate_sizing/Test_Result_cadc1006.xlsx
@@ -560,7 +560,7 @@
       </c>
       <c r="E3" s="4" t="inlineStr">
         <is>
-          <t>7.00</t>
+          <t>2400.00</t>
         </is>
       </c>
       <c r="F3" s="4" t="inlineStr">
@@ -583,27 +583,27 @@
       </c>
       <c r="C4" s="4" t="inlineStr">
         <is>
-          <t>-14460.77</t>
+          <t>-14737.89</t>
         </is>
       </c>
       <c r="D4" s="4" t="inlineStr">
         <is>
-          <t>-13024.05</t>
+          <t>-20896.53</t>
         </is>
       </c>
       <c r="E4" s="4" t="inlineStr">
         <is>
-          <t>-2107.20</t>
+          <t>-2106.73</t>
         </is>
       </c>
       <c r="F4" s="4" t="inlineStr">
         <is>
-          <t>-197592.39</t>
+          <t>-204446.91</t>
         </is>
       </c>
       <c r="G4" s="4" t="inlineStr">
         <is>
-          <t>-337088.04</t>
+          <t>-341733.09</t>
         </is>
       </c>
     </row>
@@ -616,27 +616,27 @@
       </c>
       <c r="C5" s="4" t="inlineStr">
         <is>
-          <t>-92.95</t>
+          <t>-92.56</t>
         </is>
       </c>
       <c r="D5" s="4" t="inlineStr">
         <is>
-          <t>-79.57</t>
+          <t>-113.12</t>
         </is>
       </c>
       <c r="E5" s="4" t="inlineStr">
         <is>
-          <t>-72.49</t>
+          <t>-72.51</t>
         </is>
       </c>
       <c r="F5" s="4" t="inlineStr">
         <is>
-          <t>-293.17</t>
+          <t>-290.01</t>
         </is>
       </c>
       <c r="G5" s="4" t="inlineStr">
         <is>
-          <t>-378.09</t>
+          <t>-371.63</t>
         </is>
       </c>
     </row>
@@ -649,27 +649,27 @@
       </c>
       <c r="C6" s="4" t="inlineStr">
         <is>
-          <t>7.83</t>
+          <t>7.77</t>
         </is>
       </c>
       <c r="D6" s="4" t="inlineStr">
         <is>
-          <t>4.18</t>
+          <t>4.07</t>
         </is>
       </c>
       <c r="E6" s="4" t="inlineStr">
         <is>
-          <t>1.58</t>
+          <t>1.59</t>
         </is>
       </c>
       <c r="F6" s="4" t="inlineStr">
         <is>
-          <t>12.97</t>
+          <t>9.93</t>
         </is>
       </c>
       <c r="G6" s="4" t="inlineStr">
         <is>
-          <t>11.53</t>
+          <t>9.03</t>
         </is>
       </c>
     </row>
@@ -880,27 +880,27 @@
       </c>
       <c r="C13" s="4" t="inlineStr">
         <is>
-          <t>-0.035036</t>
+          <t>-0.054870</t>
         </is>
       </c>
       <c r="D13" s="4" t="inlineStr">
         <is>
-          <t>-0.905784</t>
+          <t>-2.057749</t>
         </is>
       </c>
       <c r="E13" s="4" t="inlineStr">
         <is>
-          <t>-0.028308</t>
+          <t>-0.028078</t>
         </is>
       </c>
       <c r="F13" s="4" t="inlineStr">
         <is>
-          <t>0.003132</t>
+          <t>-0.031450</t>
         </is>
       </c>
       <c r="G13" s="4" t="inlineStr">
         <is>
-          <t>0.135664</t>
+          <t>0.123754</t>
         </is>
       </c>
     </row>
@@ -913,27 +913,27 @@
       </c>
       <c r="C14" s="4" t="inlineStr">
         <is>
-          <t>0.003356</t>
+          <t>0.011478</t>
         </is>
       </c>
       <c r="D14" s="4" t="inlineStr">
         <is>
-          <t>0.037204</t>
+          <t>0.060692</t>
         </is>
       </c>
       <c r="E14" s="4" t="inlineStr">
         <is>
-          <t>0.001724</t>
+          <t>-0.002465</t>
         </is>
       </c>
       <c r="F14" s="4" t="inlineStr">
         <is>
-          <t>0.019457</t>
+          <t>0.249519</t>
         </is>
       </c>
       <c r="G14" s="4" t="inlineStr">
         <is>
-          <t>0.096369</t>
+          <t>0.292137</t>
         </is>
       </c>
     </row>
@@ -1022,7 +1022,7 @@
       </c>
       <c r="E17" s="4" t="inlineStr">
         <is>
-          <t>0.001944</t>
+          <t>0.666667</t>
         </is>
       </c>
       <c r="F17" s="4" t="inlineStr">
@@ -1045,27 +1045,27 @@
       </c>
       <c r="C18" s="5" t="inlineStr">
         <is>
-          <t>-0.010805</t>
+          <t>-0.014868</t>
         </is>
       </c>
       <c r="D18" s="5" t="inlineStr">
         <is>
-          <t>-0.295689</t>
+          <t>-0.679606</t>
         </is>
       </c>
       <c r="E18" s="5" t="inlineStr">
         <is>
-          <t>-0.009125</t>
+          <t>-0.010429</t>
         </is>
       </c>
       <c r="F18" s="5" t="inlineStr">
         <is>
-          <t>0.007486</t>
+          <t>0.071648</t>
         </is>
       </c>
       <c r="G18" s="5" t="inlineStr">
         <is>
-          <t>0.077928</t>
+          <t>0.138482</t>
         </is>
       </c>
     </row>
@@ -1078,27 +1078,27 @@
       </c>
       <c r="C19" s="8" t="inlineStr">
         <is>
-          <t>-10.862988</t>
+          <t>-14.926663</t>
         </is>
       </c>
       <c r="D19" s="8" t="inlineStr">
         <is>
-          <t>-295.747397</t>
+          <t>-679.664773</t>
         </is>
       </c>
       <c r="E19" s="8" t="inlineStr">
         <is>
-          <t>-9.210354</t>
+          <t>-30.456009</t>
         </is>
       </c>
       <c r="F19" s="8" t="inlineStr">
         <is>
-          <t>7.426912</t>
+          <t>71.589522</t>
         </is>
       </c>
       <c r="G19" s="8" t="inlineStr">
         <is>
-          <t>77.869649</t>
+          <t>138.423419</t>
         </is>
       </c>
     </row>

--- a/ic_cad/gate_sizing/Test_Result_cadc1006.xlsx
+++ b/ic_cad/gate_sizing/Test_Result_cadc1006.xlsx
@@ -598,7 +598,7 @@
       </c>
       <c r="F4" s="4" t="inlineStr">
         <is>
-          <t>-204446.91</t>
+          <t>-212318.03</t>
         </is>
       </c>
       <c r="G4" s="4" t="inlineStr">
@@ -631,7 +631,7 @@
       </c>
       <c r="F5" s="4" t="inlineStr">
         <is>
-          <t>-290.01</t>
+          <t>-289.86</t>
         </is>
       </c>
       <c r="G5" s="4" t="inlineStr">
@@ -664,7 +664,7 @@
       </c>
       <c r="F6" s="4" t="inlineStr">
         <is>
-          <t>9.93</t>
+          <t>9.76</t>
         </is>
       </c>
       <c r="G6" s="4" t="inlineStr">
@@ -895,7 +895,7 @@
       </c>
       <c r="F13" s="4" t="inlineStr">
         <is>
-          <t>-0.031450</t>
+          <t>-0.071160</t>
         </is>
       </c>
       <c r="G13" s="4" t="inlineStr">
@@ -928,7 +928,7 @@
       </c>
       <c r="F14" s="4" t="inlineStr">
         <is>
-          <t>0.249519</t>
+          <t>0.262398</t>
         </is>
       </c>
       <c r="G14" s="4" t="inlineStr">
@@ -1060,7 +1060,7 @@
       </c>
       <c r="F18" s="5" t="inlineStr">
         <is>
-          <t>0.071648</t>
+          <t>0.062397</t>
         </is>
       </c>
       <c r="G18" s="5" t="inlineStr">
@@ -1093,7 +1093,7 @@
       </c>
       <c r="F19" s="8" t="inlineStr">
         <is>
-          <t>71.589522</t>
+          <t>62.338177</t>
         </is>
       </c>
       <c r="G19" s="8" t="inlineStr">
